--- a/analysis/gear_testing_2026/data/2026_gear_testing_haul_log.xlsx
+++ b/analysis/gear_testing_2026/data/2026_gear_testing_haul_log.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sean.rohan\Work\afsc\trawlmetrics\analysis\gear_testing_2026\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D41E6CE2-D23F-4316-A5CB-5A93E2BBA99A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEEA0BF1-4271-4EC0-9E70-680CEDCD97E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0B48783C-3736-487B-A035-F10B907419DE}"/>
+    <workbookView xWindow="30330" yWindow="3225" windowWidth="21600" windowHeight="11295" xr2:uid="{0B48783C-3736-487B-A035-F10B907419DE}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20067,7 +20067,7 @@
         <v>46247</v>
       </c>
       <c r="C368" s="6">
-        <v>0.6020833333333333</v>
+        <v>0.60243055555555558</v>
       </c>
       <c r="D368" s="1">
         <v>156</v>

--- a/analysis/gear_testing_2026/data/2026_gear_testing_haul_log.xlsx
+++ b/analysis/gear_testing_2026/data/2026_gear_testing_haul_log.xlsx
@@ -1,20 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sean.rohan\Work\afsc\trawlmetrics\analysis\gear_testing_2026\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEEA0BF1-4271-4EC0-9E70-680CEDCD97E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2D19A99-E049-449F-BD6E-0AA0E9ECB64E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30330" yWindow="3225" windowWidth="21600" windowHeight="11295" xr2:uid="{0B48783C-3736-487B-A035-F10B907419DE}"/>
+    <workbookView xWindow="32115" yWindow="1995" windowWidth="21600" windowHeight="11295" activeTab="3" xr2:uid="{0B48783C-3736-487B-A035-F10B907419DE}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="treatments" sheetId="1" r:id="rId1"/>
     <sheet name="rpms" sheetId="2" r:id="rId2"/>
+    <sheet name="door_blocks" sheetId="3" r:id="rId3"/>
+    <sheet name="bridle_blocks" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="880" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="924" uniqueCount="59">
   <si>
     <t>Haul</t>
   </si>
@@ -185,6 +187,39 @@
   <si>
     <t>NNW</t>
   </si>
+  <si>
+    <t>use_door_size</t>
+  </si>
+  <si>
+    <t>Block</t>
+  </si>
+  <si>
+    <t>Half_bobbin</t>
+  </si>
+  <si>
+    <t>Bridles_A</t>
+  </si>
+  <si>
+    <t>Bridles_B</t>
+  </si>
+  <si>
+    <t>Doors_A</t>
+  </si>
+  <si>
+    <t>Doors_B</t>
+  </si>
+  <si>
+    <t>Doors_C</t>
+  </si>
+  <si>
+    <t>Doors_D</t>
+  </si>
+  <si>
+    <t>Doors_E</t>
+  </si>
+  <si>
+    <t>Doors_F</t>
+  </si>
 </sst>
 </file>
 
@@ -222,7 +257,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -245,11 +280,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -257,6 +303,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="21" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -596,7 +643,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D2E39B9-CC01-40AE-A948-E47551FAF34F}">
-  <dimension ref="A1:U399"/>
+  <dimension ref="A1:V399"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -604,7 +651,7 @@
     <col min="7" max="7" width="13.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -668,8 +715,11 @@
       <c r="U1" s="1" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V1" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>500</v>
       </c>
@@ -731,8 +781,11 @@
       <c r="U2" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V2" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>500</v>
       </c>
@@ -776,8 +829,9 @@
       <c r="U3" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V3" s="7"/>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>500</v>
       </c>
@@ -839,8 +893,11 @@
       <c r="U4" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V4" s="7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>500</v>
       </c>
@@ -885,7 +942,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>500</v>
       </c>
@@ -930,7 +987,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>500</v>
       </c>
@@ -975,7 +1032,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>500</v>
       </c>
@@ -1037,8 +1094,11 @@
       <c r="U8" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V8" s="7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>500</v>
       </c>
@@ -1083,7 +1143,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>501</v>
       </c>
@@ -1145,8 +1205,11 @@
       <c r="U10" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V10" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>501</v>
       </c>
@@ -1191,7 +1254,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>501</v>
       </c>
@@ -1253,8 +1316,11 @@
       <c r="U12" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V12" s="7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>501</v>
       </c>
@@ -1299,7 +1365,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>501</v>
       </c>
@@ -1361,8 +1427,11 @@
       <c r="U14" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V14" s="7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>501</v>
       </c>
@@ -1407,7 +1476,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>502</v>
       </c>
@@ -1469,8 +1538,11 @@
       <c r="U16" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V16" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>502</v>
       </c>
@@ -1515,7 +1587,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>502</v>
       </c>
@@ -1577,8 +1649,11 @@
       <c r="U18" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V18" s="7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>502</v>
       </c>
@@ -1623,7 +1698,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>502</v>
       </c>
@@ -1685,8 +1760,11 @@
       <c r="U20" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V20" s="7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>502</v>
       </c>
@@ -1731,7 +1809,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>503</v>
       </c>
@@ -1793,8 +1871,11 @@
       <c r="U22" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V22" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>503</v>
       </c>
@@ -1839,7 +1920,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>503</v>
       </c>
@@ -1901,8 +1982,11 @@
       <c r="U24" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V24" s="7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>503</v>
       </c>
@@ -1947,7 +2031,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>503</v>
       </c>
@@ -2009,8 +2093,11 @@
       <c r="U26" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V26" s="7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>503</v>
       </c>
@@ -2055,7 +2142,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>503</v>
       </c>
@@ -2119,8 +2206,11 @@
       <c r="U28" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V28" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>503</v>
       </c>
@@ -2167,7 +2257,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>504</v>
       </c>
@@ -2229,8 +2319,11 @@
       <c r="U30" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V30" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>504</v>
       </c>
@@ -2275,7 +2368,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>504</v>
       </c>
@@ -2337,8 +2430,11 @@
       <c r="U32" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V32" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>504</v>
       </c>
@@ -2383,7 +2479,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>505</v>
       </c>
@@ -2445,8 +2541,11 @@
       <c r="U34" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V34" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>505</v>
       </c>
@@ -2491,7 +2590,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>505</v>
       </c>
@@ -2553,8 +2652,11 @@
       <c r="U36" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V36" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>505</v>
       </c>
@@ -2599,7 +2701,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>506</v>
       </c>
@@ -2661,8 +2763,11 @@
       <c r="U38" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="39" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V38" s="7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>506</v>
       </c>
@@ -2707,7 +2812,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>506</v>
       </c>
@@ -2769,8 +2874,11 @@
       <c r="U40" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="41" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V40" s="7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>506</v>
       </c>
@@ -2815,7 +2923,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>507</v>
       </c>
@@ -2877,8 +2985,11 @@
       <c r="U42" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V42" s="7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>507</v>
       </c>
@@ -2923,7 +3034,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>507</v>
       </c>
@@ -2986,7 +3097,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>507</v>
       </c>
@@ -3031,7 +3142,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>508</v>
       </c>
@@ -3094,7 +3205,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>508</v>
       </c>
@@ -3139,7 +3250,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>509</v>
       </c>
@@ -22276,4 +22387,475 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC69E958-EF95-4B1A-8A31-9E7D6F8AE0F8}">
+  <dimension ref="A1:C27"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B2">
+        <v>500</v>
+      </c>
+      <c r="C2">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B3">
+        <v>503</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B4">
+        <v>501</v>
+      </c>
+      <c r="C4">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5">
+        <v>502</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6">
+        <v>505</v>
+      </c>
+      <c r="C6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B7">
+        <v>506</v>
+      </c>
+      <c r="C7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>55</v>
+      </c>
+      <c r="B8">
+        <v>516</v>
+      </c>
+      <c r="C8">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>55</v>
+      </c>
+      <c r="B9">
+        <v>517</v>
+      </c>
+      <c r="C9">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>56</v>
+      </c>
+      <c r="B10">
+        <v>507</v>
+      </c>
+      <c r="C10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>56</v>
+      </c>
+      <c r="B11">
+        <v>508</v>
+      </c>
+      <c r="C11">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>56</v>
+      </c>
+      <c r="B12">
+        <v>509</v>
+      </c>
+      <c r="C12">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>56</v>
+      </c>
+      <c r="B13">
+        <v>514</v>
+      </c>
+      <c r="C13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>56</v>
+      </c>
+      <c r="B14">
+        <v>515</v>
+      </c>
+      <c r="C14">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>56</v>
+      </c>
+      <c r="B15">
+        <v>518</v>
+      </c>
+      <c r="C15">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>56</v>
+      </c>
+      <c r="B16">
+        <v>519</v>
+      </c>
+      <c r="C16">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>56</v>
+      </c>
+      <c r="B17">
+        <v>523</v>
+      </c>
+      <c r="C17">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>56</v>
+      </c>
+      <c r="B18">
+        <v>524</v>
+      </c>
+      <c r="C18">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>57</v>
+      </c>
+      <c r="B19">
+        <v>510</v>
+      </c>
+      <c r="C19">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>57</v>
+      </c>
+      <c r="B20">
+        <v>511</v>
+      </c>
+      <c r="C20">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>57</v>
+      </c>
+      <c r="B21">
+        <v>520</v>
+      </c>
+      <c r="C21">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>57</v>
+      </c>
+      <c r="B22">
+        <v>521</v>
+      </c>
+      <c r="C22">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>57</v>
+      </c>
+      <c r="B23">
+        <v>522</v>
+      </c>
+      <c r="C23">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>58</v>
+      </c>
+      <c r="B24">
+        <v>512</v>
+      </c>
+      <c r="C24">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>58</v>
+      </c>
+      <c r="B25">
+        <v>513</v>
+      </c>
+      <c r="C25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>58</v>
+      </c>
+      <c r="B26">
+        <v>525</v>
+      </c>
+      <c r="C26">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>58</v>
+      </c>
+      <c r="B27">
+        <v>526</v>
+      </c>
+      <c r="C27">
+        <v>4.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA03EE9A-06D4-447F-8DB5-3F4FEA87A0D9}">
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B2">
+        <v>512</v>
+      </c>
+      <c r="C2" t="b">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B3">
+        <v>513</v>
+      </c>
+      <c r="C3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B4">
+        <v>525</v>
+      </c>
+      <c r="C4" t="b">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B5">
+        <v>526</v>
+      </c>
+      <c r="C5" t="b">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B6">
+        <v>527</v>
+      </c>
+      <c r="C6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B7">
+        <v>528</v>
+      </c>
+      <c r="C7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>52</v>
+      </c>
+      <c r="B8">
+        <v>500</v>
+      </c>
+      <c r="C8" t="b">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>52</v>
+      </c>
+      <c r="B9">
+        <v>501</v>
+      </c>
+      <c r="C9" t="b">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>52</v>
+      </c>
+      <c r="B10">
+        <v>529</v>
+      </c>
+      <c r="C10" t="b">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>52</v>
+      </c>
+      <c r="B11">
+        <v>530</v>
+      </c>
+      <c r="C11" t="b">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>4.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/analysis/gear_testing_2026/data/2026_gear_testing_haul_log.xlsx
+++ b/analysis/gear_testing_2026/data/2026_gear_testing_haul_log.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sean.rohan\Work\afsc\trawlmetrics\analysis\gear_testing_2026\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2D19A99-E049-449F-BD6E-0AA0E9ECB64E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81509B89-57AF-41BA-8D6C-7381F1709EF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32115" yWindow="1995" windowWidth="21600" windowHeight="11295" activeTab="3" xr2:uid="{0B48783C-3736-487B-A035-F10B907419DE}"/>
+    <workbookView xWindow="4575" yWindow="4620" windowWidth="17820" windowHeight="15345" activeTab="4" xr2:uid="{0B48783C-3736-487B-A035-F10B907419DE}"/>
   </bookViews>
   <sheets>
     <sheet name="treatments" sheetId="1" r:id="rId1"/>
     <sheet name="rpms" sheetId="2" r:id="rId2"/>
     <sheet name="door_blocks" sheetId="3" r:id="rId3"/>
     <sheet name="bridle_blocks" sheetId="4" r:id="rId4"/>
+    <sheet name="catch_treatments" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="924" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="981" uniqueCount="79">
   <si>
     <t>Haul</t>
   </si>
@@ -220,6 +221,66 @@
   <si>
     <t>Doors_F</t>
   </si>
+  <si>
+    <t>Catch_2</t>
+  </si>
+  <si>
+    <t>Catch_1</t>
+  </si>
+  <si>
+    <t>Catch_3</t>
+  </si>
+  <si>
+    <t>Catch_4</t>
+  </si>
+  <si>
+    <t>Catch_5</t>
+  </si>
+  <si>
+    <t>Catch_6</t>
+  </si>
+  <si>
+    <t>Catch_7</t>
+  </si>
+  <si>
+    <t>Catch_8</t>
+  </si>
+  <si>
+    <t>Catch_9</t>
+  </si>
+  <si>
+    <t>Catch_10</t>
+  </si>
+  <si>
+    <t>Catch_11</t>
+  </si>
+  <si>
+    <t>Catch_12</t>
+  </si>
+  <si>
+    <t>Catch_13</t>
+  </si>
+  <si>
+    <t>VESSEL</t>
+  </si>
+  <si>
+    <t>CRUISE</t>
+  </si>
+  <si>
+    <t>HAUL</t>
+  </si>
+  <si>
+    <t>BLOCK</t>
+  </si>
+  <si>
+    <t>83-112</t>
+  </si>
+  <si>
+    <t>RRT</t>
+  </si>
+  <si>
+    <t>GEAR_NAME</t>
+  </si>
 </sst>
 </file>
 
@@ -228,10 +289,16 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="h:mm:ss;@"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -647,6 +714,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.5703125" customWidth="1"/>
     <col min="5" max="5" width="0" hidden="1" customWidth="1"/>
     <col min="7" max="7" width="13.5703125" customWidth="1"/>
   </cols>
@@ -5442,7 +5510,7 @@
         <v>-8</v>
       </c>
       <c r="K88" s="4">
-        <v>-12.2</v>
+        <v>12.2</v>
       </c>
       <c r="L88" s="5">
         <v>2.1</v>
@@ -22418,13 +22486,13 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B3">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="C3">
-        <v>4</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -22432,18 +22500,18 @@
         <v>54</v>
       </c>
       <c r="B4">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C4">
-        <v>4.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B5">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -22473,24 +22541,24 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B8">
-        <v>516</v>
+        <v>507</v>
       </c>
       <c r="C8">
-        <v>4.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B9">
-        <v>517</v>
+        <v>508</v>
       </c>
       <c r="C9">
-        <v>4.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -22498,7 +22566,7 @@
         <v>56</v>
       </c>
       <c r="B10">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="C10">
         <v>4</v>
@@ -22506,10 +22574,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B11">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="C11">
         <v>4</v>
@@ -22517,10 +22585,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B12">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="C12">
         <v>4</v>
@@ -22528,10 +22596,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B13">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="C13">
         <v>4</v>
@@ -22539,10 +22607,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B14">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="C14">
         <v>4</v>
@@ -22553,10 +22621,10 @@
         <v>56</v>
       </c>
       <c r="B15">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="C15">
-        <v>4.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -22564,18 +22632,18 @@
         <v>56</v>
       </c>
       <c r="B16">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="C16">
-        <v>4.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B17">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="C17">
         <v>4.5</v>
@@ -22583,10 +22651,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B18">
-        <v>524</v>
+        <v>517</v>
       </c>
       <c r="C18">
         <v>4.5</v>
@@ -22594,24 +22662,24 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B19">
-        <v>510</v>
+        <v>518</v>
       </c>
       <c r="C19">
-        <v>4</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B20">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="C20">
-        <v>4</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -22649,24 +22717,24 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B24">
-        <v>512</v>
+        <v>523</v>
       </c>
       <c r="C24">
-        <v>4</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B25">
-        <v>513</v>
+        <v>524</v>
       </c>
       <c r="C25">
-        <v>4</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -22692,6 +22760,9 @@
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C27">
+    <sortCondition ref="B2:B27"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -22858,4 +22929,477 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27646FA9-5871-4C36-9D5F-7E4A0C9008ED}">
+  <dimension ref="A1:E27"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B2">
+        <v>134</v>
+      </c>
+      <c r="C2">
+        <v>202601</v>
+      </c>
+      <c r="D2">
+        <v>601</v>
+      </c>
+      <c r="E2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B3">
+        <v>162</v>
+      </c>
+      <c r="C3">
+        <v>202601</v>
+      </c>
+      <c r="D3">
+        <v>601</v>
+      </c>
+      <c r="E3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B4">
+        <v>134</v>
+      </c>
+      <c r="C4">
+        <v>202601</v>
+      </c>
+      <c r="D4">
+        <v>602</v>
+      </c>
+      <c r="E4" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B5">
+        <v>162</v>
+      </c>
+      <c r="C5">
+        <v>202601</v>
+      </c>
+      <c r="D5">
+        <v>602</v>
+      </c>
+      <c r="E5" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B6">
+        <v>134</v>
+      </c>
+      <c r="C6">
+        <v>202601</v>
+      </c>
+      <c r="D6">
+        <v>604</v>
+      </c>
+      <c r="E6" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>61</v>
+      </c>
+      <c r="B7">
+        <v>162</v>
+      </c>
+      <c r="C7">
+        <v>202601</v>
+      </c>
+      <c r="D7">
+        <v>603</v>
+      </c>
+      <c r="E7" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>62</v>
+      </c>
+      <c r="B8">
+        <v>134</v>
+      </c>
+      <c r="C8">
+        <v>202601</v>
+      </c>
+      <c r="D8">
+        <v>605</v>
+      </c>
+      <c r="E8" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>62</v>
+      </c>
+      <c r="B9">
+        <v>162</v>
+      </c>
+      <c r="C9">
+        <v>202601</v>
+      </c>
+      <c r="D9">
+        <v>604</v>
+      </c>
+      <c r="E9" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>63</v>
+      </c>
+      <c r="B10">
+        <v>134</v>
+      </c>
+      <c r="C10">
+        <v>202601</v>
+      </c>
+      <c r="D10">
+        <v>606</v>
+      </c>
+      <c r="E10" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>63</v>
+      </c>
+      <c r="B11">
+        <v>162</v>
+      </c>
+      <c r="C11">
+        <v>202601</v>
+      </c>
+      <c r="D11">
+        <v>605</v>
+      </c>
+      <c r="E11" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>64</v>
+      </c>
+      <c r="B12">
+        <v>134</v>
+      </c>
+      <c r="C12">
+        <v>202601</v>
+      </c>
+      <c r="D12">
+        <v>607</v>
+      </c>
+      <c r="E12" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>64</v>
+      </c>
+      <c r="B13">
+        <v>162</v>
+      </c>
+      <c r="C13">
+        <v>202601</v>
+      </c>
+      <c r="D13">
+        <v>606</v>
+      </c>
+      <c r="E13" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>65</v>
+      </c>
+      <c r="B14">
+        <v>134</v>
+      </c>
+      <c r="C14">
+        <v>202601</v>
+      </c>
+      <c r="D14">
+        <v>608</v>
+      </c>
+      <c r="E14" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>65</v>
+      </c>
+      <c r="B15">
+        <v>162</v>
+      </c>
+      <c r="C15">
+        <v>202601</v>
+      </c>
+      <c r="D15">
+        <v>607</v>
+      </c>
+      <c r="E15" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>66</v>
+      </c>
+      <c r="B16">
+        <v>134</v>
+      </c>
+      <c r="C16">
+        <v>202601</v>
+      </c>
+      <c r="D16">
+        <v>609</v>
+      </c>
+      <c r="E16" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>66</v>
+      </c>
+      <c r="B17">
+        <v>162</v>
+      </c>
+      <c r="C17">
+        <v>202601</v>
+      </c>
+      <c r="D17">
+        <v>608</v>
+      </c>
+      <c r="E17" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>67</v>
+      </c>
+      <c r="B18">
+        <v>134</v>
+      </c>
+      <c r="C18">
+        <v>202601</v>
+      </c>
+      <c r="D18">
+        <v>610</v>
+      </c>
+      <c r="E18" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>67</v>
+      </c>
+      <c r="B19">
+        <v>162</v>
+      </c>
+      <c r="C19">
+        <v>202601</v>
+      </c>
+      <c r="D19">
+        <v>609</v>
+      </c>
+      <c r="E19" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>68</v>
+      </c>
+      <c r="B20">
+        <v>134</v>
+      </c>
+      <c r="C20">
+        <v>202601</v>
+      </c>
+      <c r="D20">
+        <v>611</v>
+      </c>
+      <c r="E20" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>68</v>
+      </c>
+      <c r="B21">
+        <v>162</v>
+      </c>
+      <c r="C21">
+        <v>202601</v>
+      </c>
+      <c r="D21">
+        <v>610</v>
+      </c>
+      <c r="E21" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>69</v>
+      </c>
+      <c r="B22">
+        <v>134</v>
+      </c>
+      <c r="C22">
+        <v>202601</v>
+      </c>
+      <c r="D22">
+        <v>612</v>
+      </c>
+      <c r="E22" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>69</v>
+      </c>
+      <c r="B23">
+        <v>162</v>
+      </c>
+      <c r="C23">
+        <v>202601</v>
+      </c>
+      <c r="D23">
+        <v>611</v>
+      </c>
+      <c r="E23" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>70</v>
+      </c>
+      <c r="B24">
+        <v>134</v>
+      </c>
+      <c r="C24">
+        <v>202601</v>
+      </c>
+      <c r="D24">
+        <v>613</v>
+      </c>
+      <c r="E24" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>70</v>
+      </c>
+      <c r="B25">
+        <v>162</v>
+      </c>
+      <c r="C25">
+        <v>202601</v>
+      </c>
+      <c r="D25">
+        <v>612</v>
+      </c>
+      <c r="E25" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>71</v>
+      </c>
+      <c r="B26">
+        <v>134</v>
+      </c>
+      <c r="C26">
+        <v>202601</v>
+      </c>
+      <c r="D26">
+        <v>614</v>
+      </c>
+      <c r="E26" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>71</v>
+      </c>
+      <c r="B27">
+        <v>162</v>
+      </c>
+      <c r="C27">
+        <v>202601</v>
+      </c>
+      <c r="D27">
+        <v>613</v>
+      </c>
+      <c r="E27" t="s">
+        <v>76</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:A19">
+    <sortCondition ref="A2:A19"/>
+  </sortState>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/analysis/gear_testing_2026/data/2026_gear_testing_haul_log.xlsx
+++ b/analysis/gear_testing_2026/data/2026_gear_testing_haul_log.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sean.rohan\Work\afsc\trawlmetrics\analysis\gear_testing_2026\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81509B89-57AF-41BA-8D6C-7381F1709EF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B059C03E-A1B0-4E68-8A5B-33B7490616C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4575" yWindow="4620" windowWidth="17820" windowHeight="15345" activeTab="4" xr2:uid="{0B48783C-3736-487B-A035-F10B907419DE}"/>
+    <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{0B48783C-3736-487B-A035-F10B907419DE}"/>
   </bookViews>
   <sheets>
     <sheet name="treatments" sheetId="1" r:id="rId1"/>
@@ -21455,7 +21455,7 @@
         <v>611</v>
       </c>
       <c r="B392" s="2">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="C392" s="6">
         <v>0.35093750000000001</v>
@@ -21514,7 +21514,7 @@
         <v>611</v>
       </c>
       <c r="B393" s="2">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="C393" s="6">
         <v>0.36135416666666664</v>

--- a/analysis/gear_testing_2026/data/2026_gear_testing_haul_log.xlsx
+++ b/analysis/gear_testing_2026/data/2026_gear_testing_haul_log.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sean.rohan\Work\afsc\trawlmetrics\analysis\gear_testing_2026\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ACBB70A-7A64-464D-9631-0D552B14B158}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DDAA7F7-33D5-43F0-9387-4396BE33E85D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10380" yWindow="3720" windowWidth="38700" windowHeight="15345" xr2:uid="{0B48783C-3736-487B-A035-F10B907419DE}"/>
+    <workbookView xWindow="10380" yWindow="3720" windowWidth="38700" windowHeight="15345" activeTab="2" xr2:uid="{0B48783C-3736-487B-A035-F10B907419DE}"/>
   </bookViews>
   <sheets>
     <sheet name="treatments" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1020" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1020" uniqueCount="81">
   <si>
     <t>Haul</t>
   </si>
@@ -179,9 +179,6 @@
   </si>
   <si>
     <t>NNW</t>
-  </si>
-  <si>
-    <t>Block</t>
   </si>
   <si>
     <t>Bridles_A</t>
@@ -19443,18 +19440,18 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>45</v>
+        <v>69</v>
       </c>
       <c r="B1" t="s">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="C1" t="s">
-        <v>17</v>
+        <v>80</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B2">
         <v>500</v>
@@ -19465,7 +19462,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B3">
         <v>501</v>
@@ -19476,7 +19473,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B4">
         <v>502</v>
@@ -19487,7 +19484,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B5">
         <v>503</v>
@@ -19498,7 +19495,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B6">
         <v>505</v>
@@ -19509,7 +19506,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B7">
         <v>506</v>
@@ -19520,7 +19517,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B8">
         <v>507</v>
@@ -19531,7 +19528,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B9">
         <v>508</v>
@@ -19542,7 +19539,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B10">
         <v>509</v>
@@ -19553,7 +19550,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B11">
         <v>510</v>
@@ -19564,7 +19561,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B12">
         <v>511</v>
@@ -19575,7 +19572,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B13">
         <v>512</v>
@@ -19586,7 +19583,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B14">
         <v>513</v>
@@ -19597,7 +19594,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B15">
         <v>514</v>
@@ -19608,7 +19605,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B16">
         <v>515</v>
@@ -19619,7 +19616,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B17">
         <v>516</v>
@@ -19630,7 +19627,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B18">
         <v>517</v>
@@ -19641,7 +19638,7 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B19">
         <v>518</v>
@@ -19652,7 +19649,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B20">
         <v>519</v>
@@ -19663,7 +19660,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B21">
         <v>520</v>
@@ -19674,7 +19671,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B22">
         <v>521</v>
@@ -19685,7 +19682,7 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B23">
         <v>522</v>
@@ -19696,7 +19693,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B24">
         <v>523</v>
@@ -19707,7 +19704,7 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B25">
         <v>524</v>
@@ -19718,7 +19715,7 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B26">
         <v>525</v>
@@ -19729,7 +19726,7 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B27">
         <v>526</v>
@@ -19753,49 +19750,49 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B2">
         <v>518</v>
       </c>
       <c r="C2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B3">
         <v>523</v>
       </c>
       <c r="C3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B4">
         <v>519</v>
@@ -19804,12 +19801,12 @@
         <v>43</v>
       </c>
       <c r="D4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B5">
         <v>524</v>
@@ -19818,172 +19815,172 @@
         <v>43</v>
       </c>
       <c r="D5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B6">
         <v>600</v>
       </c>
       <c r="D6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B7">
         <v>601</v>
       </c>
       <c r="D7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B8">
         <v>602</v>
       </c>
       <c r="D8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B9">
         <v>603</v>
       </c>
       <c r="D9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B10">
         <v>604</v>
       </c>
       <c r="D10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B11">
         <v>605</v>
       </c>
       <c r="D11" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B12">
         <v>606</v>
       </c>
       <c r="D12" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B13">
         <v>607</v>
       </c>
       <c r="D13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B14">
         <v>608</v>
       </c>
       <c r="D14" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B15">
         <v>609</v>
       </c>
       <c r="D15" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B16">
         <v>610</v>
       </c>
       <c r="D16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B17">
         <v>611</v>
       </c>
       <c r="D17" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B18">
         <v>612</v>
       </c>
       <c r="D18" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B19">
         <v>613</v>
       </c>
       <c r="D19" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B20">
         <v>614</v>
       </c>
       <c r="D20" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -19999,18 +19996,18 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B2">
         <v>525</v>
@@ -20021,7 +20018,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B3">
         <v>526</v>
@@ -20032,7 +20029,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B4">
         <v>527</v>
@@ -20043,7 +20040,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B5">
         <v>528</v>
@@ -20054,7 +20051,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B6">
         <v>500</v>
@@ -20065,7 +20062,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B7">
         <v>501</v>
@@ -20076,7 +20073,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B8">
         <v>529</v>
@@ -20087,7 +20084,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B9">
         <v>530</v>
@@ -20108,24 +20105,24 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C1" t="s">
         <v>67</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>68</v>
       </c>
-      <c r="D1" t="s">
-        <v>69</v>
-      </c>
       <c r="E1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B2">
         <v>134</v>
@@ -20137,12 +20134,12 @@
         <v>601</v>
       </c>
       <c r="E2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B3">
         <v>162</v>
@@ -20154,12 +20151,12 @@
         <v>601</v>
       </c>
       <c r="E3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B4">
         <v>134</v>
@@ -20171,12 +20168,12 @@
         <v>602</v>
       </c>
       <c r="E4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B5">
         <v>162</v>
@@ -20188,12 +20185,12 @@
         <v>602</v>
       </c>
       <c r="E5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B6">
         <v>134</v>
@@ -20205,12 +20202,12 @@
         <v>604</v>
       </c>
       <c r="E6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B7">
         <v>162</v>
@@ -20222,12 +20219,12 @@
         <v>603</v>
       </c>
       <c r="E7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B8">
         <v>134</v>
@@ -20239,12 +20236,12 @@
         <v>605</v>
       </c>
       <c r="E8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B9">
         <v>162</v>
@@ -20256,12 +20253,12 @@
         <v>604</v>
       </c>
       <c r="E9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B10">
         <v>134</v>
@@ -20273,12 +20270,12 @@
         <v>606</v>
       </c>
       <c r="E10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B11">
         <v>162</v>
@@ -20290,12 +20287,12 @@
         <v>605</v>
       </c>
       <c r="E11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B12">
         <v>134</v>
@@ -20307,12 +20304,12 @@
         <v>607</v>
       </c>
       <c r="E12" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B13">
         <v>162</v>
@@ -20324,12 +20321,12 @@
         <v>606</v>
       </c>
       <c r="E13" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B14">
         <v>134</v>
@@ -20341,12 +20338,12 @@
         <v>608</v>
       </c>
       <c r="E14" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B15">
         <v>162</v>
@@ -20358,12 +20355,12 @@
         <v>607</v>
       </c>
       <c r="E15" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B16">
         <v>134</v>
@@ -20375,12 +20372,12 @@
         <v>609</v>
       </c>
       <c r="E16" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B17">
         <v>162</v>
@@ -20392,12 +20389,12 @@
         <v>608</v>
       </c>
       <c r="E17" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B18">
         <v>134</v>
@@ -20409,12 +20406,12 @@
         <v>610</v>
       </c>
       <c r="E18" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B19">
         <v>162</v>
@@ -20426,12 +20423,12 @@
         <v>609</v>
       </c>
       <c r="E19" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B20">
         <v>134</v>
@@ -20443,12 +20440,12 @@
         <v>611</v>
       </c>
       <c r="E20" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B21">
         <v>162</v>
@@ -20460,12 +20457,12 @@
         <v>610</v>
       </c>
       <c r="E21" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B22">
         <v>134</v>
@@ -20477,12 +20474,12 @@
         <v>612</v>
       </c>
       <c r="E22" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B23">
         <v>162</v>
@@ -20494,12 +20491,12 @@
         <v>611</v>
       </c>
       <c r="E23" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B24">
         <v>134</v>
@@ -20511,12 +20508,12 @@
         <v>613</v>
       </c>
       <c r="E24" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B25">
         <v>162</v>
@@ -20528,12 +20525,12 @@
         <v>612</v>
       </c>
       <c r="E25" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B26">
         <v>134</v>
@@ -20545,12 +20542,12 @@
         <v>614</v>
       </c>
       <c r="E26" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B27">
         <v>162</v>
@@ -20562,7 +20559,7 @@
         <v>613</v>
       </c>
       <c r="E27" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>

--- a/analysis/gear_testing_2026/data/2026_gear_testing_haul_log.xlsx
+++ b/analysis/gear_testing_2026/data/2026_gear_testing_haul_log.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sean.rohan\Work\afsc\trawlmetrics\analysis\gear_testing_2026\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DDAA7F7-33D5-43F0-9387-4396BE33E85D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0F45EDA-C770-4E15-9B69-CF664BF67D87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10380" yWindow="3720" windowWidth="38700" windowHeight="15345" activeTab="2" xr2:uid="{0B48783C-3736-487B-A035-F10B907419DE}"/>
+    <workbookView xWindow="390" yWindow="1110" windowWidth="28410" windowHeight="15090" xr2:uid="{0B48783C-3736-487B-A035-F10B907419DE}"/>
   </bookViews>
   <sheets>
     <sheet name="treatments" sheetId="1" r:id="rId1"/>
@@ -1970,7 +1970,7 @@
         <v>2</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H28" s="4">
         <v>2.1</v>
@@ -2026,7 +2026,7 @@
         <v>2</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H29" s="4"/>
       <c r="I29" s="4"/>
@@ -3342,7 +3342,7 @@
         <v>46237</v>
       </c>
       <c r="C58" s="3">
-        <v>0.72138888888888886</v>
+        <v>0.72187500000000004</v>
       </c>
       <c r="D58" s="1">
         <v>75</v>
@@ -3354,7 +3354,7 @@
         <v>1</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="H58" s="4">
         <v>2</v>
@@ -4206,7 +4206,7 @@
         <v>0.2</v>
       </c>
       <c r="O76" s="5">
-        <v>10.1</v>
+        <v>-10.1</v>
       </c>
       <c r="P76" s="1"/>
       <c r="Q76" s="1" t="s">
@@ -4758,7 +4758,7 @@
         <v>-7.9</v>
       </c>
       <c r="O88" s="5">
-        <v>14.9</v>
+        <v>-14.9</v>
       </c>
       <c r="P88" s="1"/>
       <c r="Q88" s="1" t="s">
@@ -5310,7 +5310,7 @@
         <v>-11.8</v>
       </c>
       <c r="O100" s="5">
-        <v>26.5</v>
+        <v>-26.5</v>
       </c>
       <c r="P100" s="1"/>
       <c r="Q100" s="1" t="s">
@@ -9542,7 +9542,7 @@
         <v>-16.8</v>
       </c>
       <c r="O192" s="5">
-        <v>36.5</v>
+        <v>-36.5</v>
       </c>
       <c r="P192" s="1"/>
       <c r="Q192" s="1" t="s">
@@ -12702,7 +12702,7 @@
         <v>-4.7</v>
       </c>
       <c r="O262" s="5">
-        <v>3</v>
+        <v>-3</v>
       </c>
       <c r="P262" s="1"/>
       <c r="Q262" s="1" t="s">
@@ -16248,7 +16248,7 @@
         <v>-7.8</v>
       </c>
       <c r="O340" s="5">
-        <v>29.7</v>
+        <v>-29.7</v>
       </c>
       <c r="P340" s="1"/>
       <c r="Q340" s="1" t="s">

--- a/analysis/gear_testing_2026/data/2026_gear_testing_haul_log.xlsx
+++ b/analysis/gear_testing_2026/data/2026_gear_testing_haul_log.xlsx
@@ -8,17 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sean.rohan\Work\afsc\trawlmetrics\analysis\gear_testing_2026\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0F45EDA-C770-4E15-9B69-CF664BF67D87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{930470BA-EE52-40D2-B3F2-089DDA9EC85A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="1110" windowWidth="28410" windowHeight="15090" xr2:uid="{0B48783C-3736-487B-A035-F10B907419DE}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="38700" windowHeight="15345" activeTab="3" xr2:uid="{0B48783C-3736-487B-A035-F10B907419DE}"/>
   </bookViews>
   <sheets>
     <sheet name="treatments" sheetId="1" r:id="rId1"/>
     <sheet name="rpms" sheetId="2" r:id="rId2"/>
     <sheet name="door_blocks" sheetId="3" r:id="rId3"/>
-    <sheet name="bale_blocks" sheetId="6" r:id="rId4"/>
-    <sheet name="bridle_blocks" sheetId="4" r:id="rId5"/>
-    <sheet name="catch_treatments" sheetId="5" r:id="rId6"/>
+    <sheet name="bridle_blocks" sheetId="4" r:id="rId4"/>
+    <sheet name="door_angle_blocks" sheetId="6" r:id="rId5"/>
+    <sheet name="bale_blocks" sheetId="7" r:id="rId6"/>
+    <sheet name="catch_treatments" sheetId="5" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1020" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1038" uniqueCount="84">
   <si>
     <t>Haul</t>
   </si>
@@ -287,6 +288,15 @@
   </si>
   <si>
     <t>DOOR_SIZE_M2</t>
+  </si>
+  <si>
+    <t>DOOR_BALE_POSITION</t>
+  </si>
+  <si>
+    <t>Upper</t>
+  </si>
+  <si>
+    <t>Lower</t>
   </si>
 </sst>
 </file>
@@ -19744,6 +19754,130 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA03EE9A-06D4-447F-8DB5-3F4FEA87A0D9}">
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B2">
+        <v>525</v>
+      </c>
+      <c r="C2">
+        <v>4.5</v>
+      </c>
+      <c r="D2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B3">
+        <v>526</v>
+      </c>
+      <c r="C3">
+        <v>4.5</v>
+      </c>
+      <c r="D3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4">
+        <v>527</v>
+      </c>
+      <c r="C4">
+        <v>4.5</v>
+      </c>
+      <c r="D4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B5">
+        <v>528</v>
+      </c>
+      <c r="C5">
+        <v>4.5</v>
+      </c>
+      <c r="D5" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>46</v>
+      </c>
+      <c r="B6">
+        <v>500</v>
+      </c>
+      <c r="C6">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B7">
+        <v>501</v>
+      </c>
+      <c r="C7">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>46</v>
+      </c>
+      <c r="B8">
+        <v>529</v>
+      </c>
+      <c r="C8">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>46</v>
+      </c>
+      <c r="B9">
+        <v>530</v>
+      </c>
+      <c r="C9">
+        <v>4.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDE13C79-2DB5-44A8-B20B-72FEB8E80BF7}">
   <dimension ref="A1:D20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -19989,108 +20123,75 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA03EE9A-06D4-447F-8DB5-3F4FEA87A0D9}">
-  <dimension ref="A1:C9"/>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E569A69-79D7-48AE-BF76-E3E901760DA7}">
+  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B1" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B2">
-        <v>525</v>
-      </c>
-      <c r="C2">
-        <v>4.5</v>
+      <c r="A2">
+        <v>507</v>
+      </c>
+      <c r="B2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C2" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3">
-        <v>526</v>
-      </c>
-      <c r="C3">
-        <v>4.5</v>
+      <c r="A3">
+        <v>508</v>
+      </c>
+      <c r="B3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C3" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>45</v>
-      </c>
-      <c r="B4">
-        <v>527</v>
-      </c>
-      <c r="C4">
-        <v>4.5</v>
+      <c r="A4">
+        <v>509</v>
+      </c>
+      <c r="B4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C4" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B5">
-        <v>528</v>
-      </c>
-      <c r="C5">
-        <v>4.5</v>
+      <c r="A5">
+        <v>514</v>
+      </c>
+      <c r="B5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>46</v>
-      </c>
-      <c r="B6">
-        <v>500</v>
-      </c>
-      <c r="C6">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>46</v>
-      </c>
-      <c r="B7">
-        <v>501</v>
-      </c>
-      <c r="C7">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>46</v>
-      </c>
-      <c r="B8">
-        <v>529</v>
-      </c>
-      <c r="C8">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>46</v>
-      </c>
-      <c r="B9">
-        <v>530</v>
-      </c>
-      <c r="C9">
-        <v>4.5</v>
+      <c r="A6">
+        <v>515</v>
+      </c>
+      <c r="B6" t="s">
+        <v>74</v>
+      </c>
+      <c r="C6" t="s">
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -20098,7 +20199,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27646FA9-5871-4C36-9D5F-7E4A0C9008ED}">
   <dimension ref="A1:E27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>

--- a/analysis/gear_testing_2026/data/2026_gear_testing_haul_log.xlsx
+++ b/analysis/gear_testing_2026/data/2026_gear_testing_haul_log.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sean.rohan\Work\afsc\trawlmetrics\analysis\gear_testing_2026\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{930470BA-EE52-40D2-B3F2-089DDA9EC85A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F124D58-F65B-43B7-8B16-34C511EBD4A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1950" windowWidth="38700" windowHeight="15345" activeTab="3" xr2:uid="{0B48783C-3736-487B-A035-F10B907419DE}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0B48783C-3736-487B-A035-F10B907419DE}"/>
   </bookViews>
   <sheets>
     <sheet name="treatments" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="door_blocks" sheetId="3" r:id="rId3"/>
     <sheet name="bridle_blocks" sheetId="4" r:id="rId4"/>
     <sheet name="door_angle_blocks" sheetId="6" r:id="rId5"/>
-    <sheet name="bale_blocks" sheetId="7" r:id="rId6"/>
+    <sheet name="bail_blocks" sheetId="7" r:id="rId6"/>
     <sheet name="catch_treatments" sheetId="5" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -143,16 +143,7 @@
     <t>event</t>
   </si>
   <si>
-    <t>rpm</t>
-  </si>
-  <si>
-    <t>speed_knots</t>
-  </si>
-  <si>
     <t>set</t>
-  </si>
-  <si>
-    <t>tension</t>
   </si>
   <si>
     <t>on bottom</t>
@@ -162,9 +153,6 @@
   </si>
   <si>
     <t>current_direction</t>
-  </si>
-  <si>
-    <t>current_speed</t>
   </si>
   <si>
     <t>NE</t>
@@ -290,13 +278,25 @@
     <t>DOOR_SIZE_M2</t>
   </si>
   <si>
-    <t>DOOR_BALE_POSITION</t>
-  </si>
-  <si>
     <t>Upper</t>
   </si>
   <si>
     <t>Lower</t>
+  </si>
+  <si>
+    <t>DOOR_BAIL_POSITION</t>
+  </si>
+  <si>
+    <t>rpms</t>
+  </si>
+  <si>
+    <t>winch_tension_side</t>
+  </si>
+  <si>
+    <t>current_speed_knots</t>
+  </si>
+  <si>
+    <t>vessel_speed_knots</t>
   </si>
 </sst>
 </file>
@@ -9625,15 +9625,27 @@
       <c r="H194" s="4">
         <v>1.5</v>
       </c>
-      <c r="I194" s="4"/>
-      <c r="J194" s="4"/>
-      <c r="K194" s="4"/>
+      <c r="I194" s="4">
+        <v>26.3</v>
+      </c>
+      <c r="J194" s="4">
+        <v>-29.9</v>
+      </c>
+      <c r="K194" s="4">
+        <v>57.7</v>
+      </c>
       <c r="L194" s="5">
         <v>1.4</v>
       </c>
-      <c r="M194" s="5"/>
-      <c r="N194" s="5"/>
-      <c r="O194" s="5"/>
+      <c r="M194" s="5">
+        <v>26.1</v>
+      </c>
+      <c r="N194" s="5">
+        <v>-24.5</v>
+      </c>
+      <c r="O194" s="5">
+        <v>-40.299999999999997</v>
+      </c>
       <c r="P194" s="1"/>
       <c r="Q194" s="1" t="s">
         <v>26</v>
@@ -9703,13 +9715,25 @@
         <v>18</v>
       </c>
       <c r="H196" s="4"/>
-      <c r="I196" s="4"/>
-      <c r="J196" s="4"/>
-      <c r="K196" s="4"/>
+      <c r="I196" s="4">
+        <v>27.4</v>
+      </c>
+      <c r="J196" s="4">
+        <v>33.299999999999997</v>
+      </c>
+      <c r="K196" s="4">
+        <v>62.5</v>
+      </c>
       <c r="L196" s="5"/>
-      <c r="M196" s="5"/>
-      <c r="N196" s="5"/>
-      <c r="O196" s="5"/>
+      <c r="M196" s="5">
+        <v>27.3</v>
+      </c>
+      <c r="N196" s="5">
+        <v>-34.799999999999997</v>
+      </c>
+      <c r="O196" s="5">
+        <v>-64.5</v>
+      </c>
       <c r="P196" s="1"/>
       <c r="Q196" s="1" t="s">
         <v>26</v>
@@ -9779,13 +9803,25 @@
         <v>18</v>
       </c>
       <c r="H198" s="4"/>
-      <c r="I198" s="4"/>
-      <c r="J198" s="4"/>
-      <c r="K198" s="4"/>
+      <c r="I198" s="4">
+        <v>25.9</v>
+      </c>
+      <c r="J198" s="4">
+        <v>-10.8</v>
+      </c>
+      <c r="K198" s="4">
+        <v>17.399999999999999</v>
+      </c>
       <c r="L198" s="5"/>
-      <c r="M198" s="5"/>
-      <c r="N198" s="5"/>
-      <c r="O198" s="5"/>
+      <c r="M198" s="5">
+        <v>26</v>
+      </c>
+      <c r="N198" s="5">
+        <v>-10.8</v>
+      </c>
+      <c r="O198" s="5">
+        <v>-15</v>
+      </c>
       <c r="P198" s="1"/>
       <c r="Q198" s="1" t="s">
         <v>26</v>
@@ -9855,13 +9891,25 @@
         <v>18</v>
       </c>
       <c r="H200" s="4"/>
-      <c r="I200" s="4"/>
-      <c r="J200" s="4"/>
-      <c r="K200" s="4"/>
+      <c r="I200" s="4">
+        <v>24</v>
+      </c>
+      <c r="J200" s="4">
+        <v>-19.3</v>
+      </c>
+      <c r="K200" s="4">
+        <v>38.1</v>
+      </c>
       <c r="L200" s="5"/>
-      <c r="M200" s="5"/>
-      <c r="N200" s="5"/>
-      <c r="O200" s="5"/>
+      <c r="M200" s="5">
+        <v>24.3</v>
+      </c>
+      <c r="N200" s="5">
+        <v>-21.3</v>
+      </c>
+      <c r="O200" s="5">
+        <v>-42.6</v>
+      </c>
       <c r="P200" s="1"/>
       <c r="Q200" s="1" t="s">
         <v>26</v>
@@ -18853,6 +18901,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB2C6B0C-F792-4299-933F-BD3DD2A25E4D}">
   <dimension ref="A1:G28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="17.5703125" customWidth="1"/>
+    <col min="4" max="4" width="13.42578125" customWidth="1"/>
+    <col min="6" max="6" width="9.140625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -18862,19 +18915,19 @@
         <v>31</v>
       </c>
       <c r="C1" t="s">
-        <v>32</v>
+        <v>80</v>
       </c>
       <c r="D1" t="s">
-        <v>33</v>
+        <v>83</v>
       </c>
       <c r="E1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F1" t="s">
         <v>35</v>
       </c>
-      <c r="F1" t="s">
-        <v>38</v>
-      </c>
       <c r="G1" t="s">
-        <v>39</v>
+        <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -18882,7 +18935,7 @@
         <v>606</v>
       </c>
       <c r="B2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C2">
         <v>1300</v>
@@ -18894,7 +18947,7 @@
         <v>2.7</v>
       </c>
       <c r="F2" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="G2">
         <v>0.5</v>
@@ -18905,7 +18958,7 @@
         <v>606</v>
       </c>
       <c r="B3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C3">
         <v>1215</v>
@@ -18917,7 +18970,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="F3" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="G3">
         <v>0.5</v>
@@ -18928,7 +18981,7 @@
         <v>606</v>
       </c>
       <c r="B4" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C4">
         <v>1350</v>
@@ -18940,7 +18993,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="F4" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="G4">
         <v>0.5</v>
@@ -18951,7 +19004,7 @@
         <v>607</v>
       </c>
       <c r="B5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C5">
         <v>1250</v>
@@ -18963,7 +19016,7 @@
         <v>3.9</v>
       </c>
       <c r="F5" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G5">
         <v>0.7</v>
@@ -18974,7 +19027,7 @@
         <v>607</v>
       </c>
       <c r="B6" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C6">
         <v>1055</v>
@@ -18983,7 +19036,7 @@
         <v>3</v>
       </c>
       <c r="F6" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G6">
         <v>0.7</v>
@@ -18994,7 +19047,7 @@
         <v>607</v>
       </c>
       <c r="B7" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C7">
         <v>1300</v>
@@ -19006,7 +19059,7 @@
         <v>2.4</v>
       </c>
       <c r="F7" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G7">
         <v>0.7</v>
@@ -19017,7 +19070,7 @@
         <v>608</v>
       </c>
       <c r="B8" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C8">
         <v>1225</v>
@@ -19026,7 +19079,7 @@
         <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -19037,7 +19090,7 @@
         <v>608</v>
       </c>
       <c r="B9" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C9">
         <v>1025</v>
@@ -19049,7 +19102,7 @@
         <v>3.6</v>
       </c>
       <c r="F9" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -19060,7 +19113,7 @@
         <v>608</v>
       </c>
       <c r="B10" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C10">
         <v>1300</v>
@@ -19072,7 +19125,7 @@
         <v>2.6</v>
       </c>
       <c r="F10" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -19083,7 +19136,7 @@
         <v>609</v>
       </c>
       <c r="B11" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C11">
         <v>1200</v>
@@ -19092,7 +19145,7 @@
         <v>4.5</v>
       </c>
       <c r="F11" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="G11">
         <v>0.9</v>
@@ -19103,7 +19156,7 @@
         <v>609</v>
       </c>
       <c r="B12" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C12">
         <v>1080</v>
@@ -19112,7 +19165,7 @@
         <v>3</v>
       </c>
       <c r="F12" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="G12">
         <v>0.9</v>
@@ -19123,7 +19176,7 @@
         <v>609</v>
       </c>
       <c r="B13" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C13">
         <v>1300</v>
@@ -19132,7 +19185,7 @@
         <v>2.4</v>
       </c>
       <c r="F13" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="G13">
         <v>0.9</v>
@@ -19143,7 +19196,7 @@
         <v>610</v>
       </c>
       <c r="B14" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C14">
         <v>1310</v>
@@ -19152,7 +19205,7 @@
         <v>4</v>
       </c>
       <c r="F14" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="G14">
         <v>1</v>
@@ -19163,7 +19216,7 @@
         <v>610</v>
       </c>
       <c r="B15" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C15">
         <v>1335</v>
@@ -19172,7 +19225,7 @@
         <v>3.9</v>
       </c>
       <c r="F15" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -19183,7 +19236,7 @@
         <v>610</v>
       </c>
       <c r="B16" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C16">
         <v>1425</v>
@@ -19192,7 +19245,7 @@
         <v>2</v>
       </c>
       <c r="F16" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -19203,7 +19256,7 @@
         <v>611</v>
       </c>
       <c r="B17" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C17">
         <v>1300</v>
@@ -19212,7 +19265,7 @@
         <v>4.2</v>
       </c>
       <c r="F17" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="G17">
         <v>0.3</v>
@@ -19223,7 +19276,7 @@
         <v>611</v>
       </c>
       <c r="B18" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C18">
         <v>1290</v>
@@ -19232,7 +19285,7 @@
         <v>3</v>
       </c>
       <c r="F18" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="G18">
         <v>0.3</v>
@@ -19243,7 +19296,7 @@
         <v>611</v>
       </c>
       <c r="B19" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C19">
         <v>1380</v>
@@ -19252,7 +19305,7 @@
         <v>1.8</v>
       </c>
       <c r="F19" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="G19">
         <v>0.3</v>
@@ -19263,7 +19316,7 @@
         <v>612</v>
       </c>
       <c r="B20" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C20">
         <v>1300</v>
@@ -19272,7 +19325,7 @@
         <v>4</v>
       </c>
       <c r="F20" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="G20">
         <v>0.5</v>
@@ -19283,7 +19336,7 @@
         <v>612</v>
       </c>
       <c r="B21" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C21">
         <v>1350</v>
@@ -19292,7 +19345,7 @@
         <v>3</v>
       </c>
       <c r="F21" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="G21">
         <v>0.5</v>
@@ -19303,7 +19356,7 @@
         <v>612</v>
       </c>
       <c r="B22" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C22">
         <v>1450</v>
@@ -19312,7 +19365,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="F22" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="G22">
         <v>0.5</v>
@@ -19323,7 +19376,7 @@
         <v>613</v>
       </c>
       <c r="B23" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C23">
         <v>1370</v>
@@ -19332,7 +19385,7 @@
         <v>4</v>
       </c>
       <c r="F23" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="G23">
         <v>0.6</v>
@@ -19343,7 +19396,7 @@
         <v>613</v>
       </c>
       <c r="B24" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C24">
         <v>1375</v>
@@ -19352,7 +19405,7 @@
         <v>3</v>
       </c>
       <c r="F24" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="G24">
         <v>0.6</v>
@@ -19363,7 +19416,7 @@
         <v>613</v>
       </c>
       <c r="B25" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C25">
         <v>1480</v>
@@ -19372,7 +19425,7 @@
         <v>2.1</v>
       </c>
       <c r="F25" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="G25">
         <v>0.6</v>
@@ -19383,7 +19436,7 @@
         <v>614</v>
       </c>
       <c r="B26" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C26">
         <v>1340</v>
@@ -19392,7 +19445,7 @@
         <v>4</v>
       </c>
       <c r="F26" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="G26">
         <v>0.6</v>
@@ -19403,7 +19456,7 @@
         <v>614</v>
       </c>
       <c r="B27" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C27">
         <v>1370</v>
@@ -19412,7 +19465,7 @@
         <v>3</v>
       </c>
       <c r="F27" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="G27">
         <v>0.6</v>
@@ -19423,7 +19476,7 @@
         <v>614</v>
       </c>
       <c r="B28" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C28">
         <v>1460</v>
@@ -19432,7 +19485,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="F28" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="G28">
         <v>0.6</v>
@@ -19450,18 +19503,18 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C1" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B2">
         <v>500</v>
@@ -19472,7 +19525,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B3">
         <v>501</v>
@@ -19483,7 +19536,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B4">
         <v>502</v>
@@ -19494,7 +19547,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B5">
         <v>503</v>
@@ -19505,7 +19558,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B6">
         <v>505</v>
@@ -19516,7 +19569,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B7">
         <v>506</v>
@@ -19527,7 +19580,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B8">
         <v>507</v>
@@ -19538,7 +19591,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B9">
         <v>508</v>
@@ -19549,7 +19602,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B10">
         <v>509</v>
@@ -19560,7 +19613,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B11">
         <v>510</v>
@@ -19571,7 +19624,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B12">
         <v>511</v>
@@ -19582,7 +19635,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B13">
         <v>512</v>
@@ -19593,7 +19646,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B14">
         <v>513</v>
@@ -19604,7 +19657,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B15">
         <v>514</v>
@@ -19615,7 +19668,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B16">
         <v>515</v>
@@ -19626,7 +19679,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B17">
         <v>516</v>
@@ -19637,7 +19690,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B18">
         <v>517</v>
@@ -19648,7 +19701,7 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B19">
         <v>518</v>
@@ -19659,7 +19712,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B20">
         <v>519</v>
@@ -19670,7 +19723,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B21">
         <v>520</v>
@@ -19681,7 +19734,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B22">
         <v>521</v>
@@ -19692,7 +19745,7 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B23">
         <v>522</v>
@@ -19703,7 +19756,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B24">
         <v>523</v>
@@ -19714,7 +19767,7 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B25">
         <v>524</v>
@@ -19725,7 +19778,7 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B26">
         <v>525</v>
@@ -19736,7 +19789,7 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B27">
         <v>526</v>
@@ -19760,21 +19813,21 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1" t="s">
         <v>69</v>
-      </c>
-      <c r="B1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D1" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B2">
         <v>525</v>
@@ -19783,12 +19836,12 @@
         <v>4.5</v>
       </c>
       <c r="D2" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B3">
         <v>526</v>
@@ -19797,12 +19850,12 @@
         <v>4.5</v>
       </c>
       <c r="D3" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B4">
         <v>527</v>
@@ -19811,12 +19864,12 @@
         <v>4.5</v>
       </c>
       <c r="D4" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B5">
         <v>528</v>
@@ -19825,12 +19878,12 @@
         <v>4.5</v>
       </c>
       <c r="D5" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B6">
         <v>500</v>
@@ -19841,7 +19894,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B7">
         <v>501</v>
@@ -19852,7 +19905,7 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B8">
         <v>529</v>
@@ -19863,7 +19916,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B9">
         <v>530</v>
@@ -19884,237 +19937,237 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1" t="s">
         <v>69</v>
       </c>
-      <c r="B1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>73</v>
-      </c>
-      <c r="D1" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B2">
         <v>518</v>
       </c>
       <c r="C2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D2" t="s">
         <v>74</v>
-      </c>
-      <c r="D2" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B3">
         <v>523</v>
       </c>
       <c r="C3" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D3" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B4">
         <v>519</v>
       </c>
       <c r="C4" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D4" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B5">
         <v>524</v>
       </c>
       <c r="C5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D5" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B6">
         <v>600</v>
       </c>
       <c r="D6" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B7">
         <v>601</v>
       </c>
       <c r="D7" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B8">
         <v>602</v>
       </c>
       <c r="D8" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B9">
         <v>603</v>
       </c>
       <c r="D9" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B10">
         <v>604</v>
       </c>
       <c r="D10" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B11">
         <v>605</v>
       </c>
       <c r="D11" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B12">
         <v>606</v>
       </c>
       <c r="D12" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B13">
         <v>607</v>
       </c>
       <c r="D13" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B14">
         <v>608</v>
       </c>
       <c r="D14" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B15">
         <v>609</v>
       </c>
       <c r="D15" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B16">
         <v>610</v>
       </c>
       <c r="D16" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B17">
         <v>611</v>
       </c>
       <c r="D17" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B18">
         <v>612</v>
       </c>
       <c r="D18" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B19">
         <v>613</v>
       </c>
       <c r="D19" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B20">
         <v>614</v>
       </c>
       <c r="D20" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -20130,13 +20183,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B1" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -20144,10 +20197,10 @@
         <v>507</v>
       </c>
       <c r="B2" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -20155,10 +20208,10 @@
         <v>508</v>
       </c>
       <c r="B3" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C3" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -20166,10 +20219,10 @@
         <v>509</v>
       </c>
       <c r="B4" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C4" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -20177,10 +20230,10 @@
         <v>514</v>
       </c>
       <c r="B5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C5" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -20188,10 +20241,10 @@
         <v>515</v>
       </c>
       <c r="B6" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C6" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -20206,24 +20259,24 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B1" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C1" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1" t="s">
         <v>68</v>
-      </c>
-      <c r="E1" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B2">
         <v>134</v>
@@ -20235,12 +20288,12 @@
         <v>601</v>
       </c>
       <c r="E2" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B3">
         <v>162</v>
@@ -20252,12 +20305,12 @@
         <v>601</v>
       </c>
       <c r="E3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B4">
         <v>134</v>
@@ -20269,12 +20322,12 @@
         <v>602</v>
       </c>
       <c r="E4" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B5">
         <v>162</v>
@@ -20286,12 +20339,12 @@
         <v>602</v>
       </c>
       <c r="E5" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B6">
         <v>134</v>
@@ -20303,12 +20356,12 @@
         <v>604</v>
       </c>
       <c r="E6" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B7">
         <v>162</v>
@@ -20320,12 +20373,12 @@
         <v>603</v>
       </c>
       <c r="E7" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B8">
         <v>134</v>
@@ -20337,12 +20390,12 @@
         <v>605</v>
       </c>
       <c r="E8" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B9">
         <v>162</v>
@@ -20354,12 +20407,12 @@
         <v>604</v>
       </c>
       <c r="E9" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B10">
         <v>134</v>
@@ -20371,12 +20424,12 @@
         <v>606</v>
       </c>
       <c r="E10" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B11">
         <v>162</v>
@@ -20388,12 +20441,12 @@
         <v>605</v>
       </c>
       <c r="E11" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B12">
         <v>134</v>
@@ -20405,12 +20458,12 @@
         <v>607</v>
       </c>
       <c r="E12" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B13">
         <v>162</v>
@@ -20422,12 +20475,12 @@
         <v>606</v>
       </c>
       <c r="E13" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B14">
         <v>134</v>
@@ -20439,12 +20492,12 @@
         <v>608</v>
       </c>
       <c r="E14" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B15">
         <v>162</v>
@@ -20456,12 +20509,12 @@
         <v>607</v>
       </c>
       <c r="E15" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="B16">
         <v>134</v>
@@ -20473,12 +20526,12 @@
         <v>609</v>
       </c>
       <c r="E16" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="B17">
         <v>162</v>
@@ -20490,12 +20543,12 @@
         <v>608</v>
       </c>
       <c r="E17" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="B18">
         <v>134</v>
@@ -20507,12 +20560,12 @@
         <v>610</v>
       </c>
       <c r="E18" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="B19">
         <v>162</v>
@@ -20524,12 +20577,12 @@
         <v>609</v>
       </c>
       <c r="E19" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B20">
         <v>134</v>
@@ -20541,12 +20594,12 @@
         <v>611</v>
       </c>
       <c r="E20" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B21">
         <v>162</v>
@@ -20558,12 +20611,12 @@
         <v>610</v>
       </c>
       <c r="E21" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B22">
         <v>134</v>
@@ -20575,12 +20628,12 @@
         <v>612</v>
       </c>
       <c r="E22" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B23">
         <v>162</v>
@@ -20592,12 +20645,12 @@
         <v>611</v>
       </c>
       <c r="E23" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B24">
         <v>134</v>
@@ -20609,12 +20662,12 @@
         <v>613</v>
       </c>
       <c r="E24" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B25">
         <v>162</v>
@@ -20626,12 +20679,12 @@
         <v>612</v>
       </c>
       <c r="E25" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B26">
         <v>134</v>
@@ -20643,12 +20696,12 @@
         <v>614</v>
       </c>
       <c r="E26" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B27">
         <v>162</v>
@@ -20660,7 +20713,7 @@
         <v>613</v>
       </c>
       <c r="E27" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
